--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6603-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6603-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C346EE-2092-4917-B0DE-A847E5387E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A007AA1-F02A-463F-8628-C4B0C0767D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{65558A73-153D-4A66-8B9B-B76CCD7C13D6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{CE060DA8-6D3D-4689-8C87-D03A4F38671E}"/>
   </bookViews>
   <sheets>
     <sheet name="6603-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1553,26 +1553,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C570810-D01D-45B9-B058-FD59531240BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247EF09E-CA5C-49DF-A81E-0AC96B851B93}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1762,7 +1762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2023</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2022</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2020</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2019</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2018</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2017</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2016</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2015</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2014</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2013</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2012</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2011</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2010</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="20" t="s">
@@ -3460,7 +3460,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2009</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2008</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2007</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2006</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2005</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2004</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2003</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2002</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2001</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>2000</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1999</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1998</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1997</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39" t="s">
         <v>60</v>
       </c>
